--- a/templates/office/EMP_TST_020_통합테스트시나리오.xlsx
+++ b/templates/office/EMP_TST_020_통합테스트시나리오.xlsx
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="135" t="n"/>
@@ -2613,7 +2613,7 @@
     <row r="22" ht="25.5" customHeight="1" s="134">
       <c r="C22" s="138" t="inlineStr">
         <is>
-          <t>그로브소프트</t>
+          <t>엠파시</t>
         </is>
       </c>
       <c r="D22" s="139" t="n"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 RA팀</t>
+          <t>한빛글로벌 RA팀</t>
         </is>
       </c>
       <c r="G5" s="146" t="inlineStr">
@@ -3240,7 +3240,7 @@
     <row r="21" ht="22.5" customHeight="1" s="134">
       <c r="A21" s="154" t="inlineStr">
         <is>
-          <t>4. 화장품 표시광고 금지/주의 표현 룰사전 40종 및 식약처 행정처분 판례 1,200건 임베딩 완료 상태</t>
+          <t>4. 제품 표시·광고 금지/주의 표현 룰사전 40종 및 식약처 행정처분 판례 1,200건 임베딩 완료 상태</t>
         </is>
       </c>
       <c r="B21" s="136" t="n"/>
@@ -3447,7 +3447,7 @@
       <c r="D30" s="198" t="n"/>
       <c r="E30" s="173" t="inlineStr">
         <is>
-          <t>브랜드(설화수/헤라 등), 제품명, 매체구분(상세페이지, SNS, 배너) 입력 폼 활성화</t>
+          <t>브랜드(루미에르/벨르코어 등), 제품명, 매체구분(상세페이지, SNS, 배너) 입력 폼 활성화</t>
         </is>
       </c>
       <c r="F30" s="199" t="n"/>
@@ -3706,7 +3706,7 @@
       <c r="D37" s="198" t="n"/>
       <c r="E37" s="171" t="inlineStr">
         <is>
-          <t>금지(BAN) 등급 즉시 분류 및 관련 법령(화장품법 제13조) 위반 태그 자동 부여</t>
+          <t>금지(BAN) 등급 즉시 분류 및 관련 법령(표시·광고 공정화법 제3조) 위반 태그 자동 부여</t>
         </is>
       </c>
       <c r="F37" s="199" t="n"/>

--- a/templates/office/EMP_TST_020_통합테스트시나리오.xlsx
+++ b/templates/office/EMP_TST_020_통합테스트시나리오.xlsx
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="135" t="n"/>
@@ -2619,7 +2619,7 @@
       <c r="D22" s="139" t="n"/>
       <c r="E22" s="140" t="inlineStr">
         <is>
-          <t>고객사명</t>
+          <t>주식회사 한빛글로벌</t>
         </is>
       </c>
       <c r="F22" s="141" t="n"/>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D4" s="28" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" s="29" t="inlineStr">
@@ -2916,7 +2916,7 @@
     <row r="1" ht="30" customHeight="1" s="134">
       <c r="A1" s="104" t="inlineStr">
         <is>
-          <t>광고심의.[SyncGuard AI] 통합 테스트 시나리오 명세서</t>
+          <t>계약·규격검증.[SyncFlow AI] 통합 테스트 시나리오 명세서</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>한빛글로벌 RA팀</t>
+          <t>한빛글로벌 QA팀</t>
         </is>
       </c>
       <c r="G5" s="146" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="8" ht="22.5" customHeight="1" s="134">
       <c r="A8" s="149" t="inlineStr">
         <is>
-          <t>• 대상 시스템: SyncGuard AI (Spring Boot 3.3.5, Vue 3 Vben, PostgreSQL 16 + pgvector)</t>
+          <t>• 대상 시스템: SyncFlow AI (Spring Boot 3.3.5, Vue 3 Vben, PostgreSQL 16 + pgvector)</t>
         </is>
       </c>
       <c r="B8" s="150" t="n"/>
@@ -3040,7 +3040,7 @@
     <row r="9" ht="22.5" customHeight="1" s="134">
       <c r="A9" s="152" t="inlineStr">
         <is>
-          <t>• 연계 시스템: 사내 SSO (OIDC/SAML), MarketingHub 광고심의, ProductLab 전성분·실증DB ([Option] KT레몬), ProductLab 효능실증DB</t>
+          <t>• 연계 시스템: 사내 SSO (OIDC/SAML), SRM-Portal 계약·규격검증, PLM-Nexus 자재BOM·시험검증DB ([Option] HB-Monitor), PLM-Nexus 성능규격시험검증DB</t>
         </is>
       </c>
       <c r="B9" s="136" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="10" ht="22.5" customHeight="1" s="134">
       <c r="A10" s="154" t="inlineStr">
         <is>
-          <t>• 주요 기능: PPTX/이미지 시안 업로드, 비정형 OCR 추출, 3단계 AI 심의(룰/RAG/Agent), 대체표현 승인, RA 심의 확정, 감사로그</t>
+          <t>• 주요 기능: PPTX/이미지 계약·도서 업로드, 비정형 OCR 추출, 3단계 AI 검증(룰/RAG/Agent), 대체표현 승인, QA 검증 확정, 감사로그</t>
         </is>
       </c>
       <c r="B10" s="136" t="n"/>
@@ -3108,7 +3108,7 @@
     <row r="13" ht="22.5" customHeight="1" s="134">
       <c r="A13" s="155" t="inlineStr">
         <is>
-          <t>마케터의 시안 업로드부터 OCR 텍스트 추출, 사내외 규제 DB 및 실증자료 연계, 3단계 점진적 AI 판정,</t>
+          <t>구매담당자의 계약·도서 업로드부터 OCR 텍스트 추출, 사내외 규제 DB 및 시험성적서 연계, 3단계 점진적 AI 판정,</t>
         </is>
       </c>
       <c r="B13" s="136" t="n"/>
@@ -3125,7 +3125,7 @@
     <row r="14" ht="22.5" customHeight="1" s="134">
       <c r="A14" s="156" t="inlineStr">
         <is>
-          <t>Side-by-Side 대조 및 대체 표현 승인, RA 심의 확정, MarketingHub 최종 회신 및 위변조 방지 불변 감사로그 적재까지</t>
+          <t>Side-by-Side 대조 및 대체 표현 승인, QA 검증 확정, SRM-Portal 최종 회신 및 위변조 방지 불변 감사로그 적재까지</t>
         </is>
       </c>
       <c r="B14" s="136" t="n"/>
@@ -3142,7 +3142,7 @@
     <row r="15" ht="22.5" customHeight="1" s="134">
       <c r="A15" s="154" t="inlineStr">
         <is>
-          <t>전체 화장품 광고표현 심의 라이프사이클의 기능, 연계, 무결성을 E2E 관점에서 완벽하게 검증한다.</t>
+          <t>전체 전장부품 구매계약표현 검증 라이프사이클의 기능, 연계, 무결성을 E2E 관점에서 완벽하게 검증한다.</t>
         </is>
       </c>
       <c r="B15" s="136" t="n"/>
@@ -3206,7 +3206,7 @@
     <row r="19" ht="22.5" customHeight="1" s="134">
       <c r="A19" s="152" t="inlineStr">
         <is>
-          <t>2. 사내 SSO, MarketingHub, KT 레몬, ProductLab 모의 인터페이스 엔드포인트 정상 활성화 상태</t>
+          <t>2. 사내 SSO, SRM-Portal, HB-Monitor, PLM-Nexus 모의 인터페이스 엔드포인트 정상 활성화 상태</t>
         </is>
       </c>
       <c r="B19" s="136" t="n"/>
@@ -3223,7 +3223,7 @@
     <row r="20" ht="22.5" customHeight="1" s="134">
       <c r="A20" s="154" t="inlineStr">
         <is>
-          <t>3. 마케터 및 RA 전문가 등 역할별 테스트 계정 및 권한 사전 발급 완료</t>
+          <t>3. 구매담당자 및 법무·QA 전문위원 등 역할별 테스트 계정 및 권한 사전 발급 완료</t>
         </is>
       </c>
       <c r="B20" s="136" t="n"/>
@@ -3240,7 +3240,7 @@
     <row r="21" ht="22.5" customHeight="1" s="134">
       <c r="A21" s="154" t="inlineStr">
         <is>
-          <t>4. 제품 표시·광고 금지/주의 표현 룰사전 40종 및 식약처 행정처분 판례 1,200건 임베딩 완료 상태</t>
+          <t>4. 구매계약·기술규격 금지/주의 표현 룰사전 40종 및 공정위·표준원 하도급 심결례 1,200건 임베딩 완료 상태</t>
         </is>
       </c>
       <c r="B21" s="136" t="n"/>
@@ -3367,13 +3367,13 @@
       </c>
       <c r="C28" s="171" t="inlineStr">
         <is>
-          <t>사내망 브라우저에서 사내 포털 로그인 후 SyncGuard AI 접근</t>
+          <t>사내망 브라우저에서 사내 포털 로그인 후 SyncFlow AI 접근</t>
         </is>
       </c>
       <c r="D28" s="198" t="n"/>
       <c r="E28" s="173" t="inlineStr">
         <is>
-          <t>OIDC SSO 토큰 검증 성공 및 마케터 세션(사번, 성명, 부서) 정상 생성</t>
+          <t>OIDC SSO 토큰 검증 성공 및 구매담당자 세션(사번, 성명, 부서) 정상 생성</t>
         </is>
       </c>
       <c r="F28" s="199" t="n"/>
@@ -3404,13 +3404,13 @@
       </c>
       <c r="C29" s="171" t="inlineStr">
         <is>
-          <t>심의 포털 대시보드 메인 화면 접근</t>
+          <t>검증 포털 대시보드 메인 화면 접근</t>
         </is>
       </c>
       <c r="D29" s="198" t="n"/>
       <c r="E29" s="173" t="inlineStr">
         <is>
-          <t>나의 심의 진행현황(작성중, 심의중, 완료) 및 최근 반려/경고 통계 정상 표시</t>
+          <t>나의 검증 진행현황(작성중, 검증중, 완료) 및 최근 반려/경고 통계 정상 표시</t>
         </is>
       </c>
       <c r="F29" s="199" t="n"/>
@@ -3436,18 +3436,18 @@
       </c>
       <c r="B30" s="170" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰 등록</t>
+          <t>신규 검증 요청 등록</t>
         </is>
       </c>
       <c r="C30" s="171" t="inlineStr">
         <is>
-          <t>광고 심의 등록 버튼 클릭</t>
+          <t>계약·규격 검증 등록 버튼 클릭</t>
         </is>
       </c>
       <c r="D30" s="198" t="n"/>
       <c r="E30" s="173" t="inlineStr">
         <is>
-          <t>브랜드(루미에르/벨르코어 등), 제품명, 매체구분(상세페이지, SNS, 배너) 입력 폼 활성화</t>
+          <t>사업본부(전장시스템본부/정밀기계본부 등), 제품명, 매체구분(물품공급계약서, 기술시방서, CAD 도면) 입력 폼 활성화</t>
         </is>
       </c>
       <c r="F30" s="199" t="n"/>
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B31" s="170" t="inlineStr">
         <is>
-          <t>시안 파일 첨부 (PPTX)</t>
+          <t>계약·도서 파일 첨부 (PPTX)</t>
         </is>
       </c>
       <c r="C31" s="171" t="inlineStr">
         <is>
-          <t>30MB 이하 규격의 복합 상세페이지 PPTX 시안 드래그 앤 드롭 업로드</t>
+          <t>30MB 이하 규격의 복합 기술시방서 PPTX 계약·도서 드래그 앤 드롭 업로드</t>
         </is>
       </c>
       <c r="D31" s="198" t="n"/>
@@ -3510,12 +3510,12 @@
       </c>
       <c r="B32" s="170" t="inlineStr">
         <is>
-          <t>시안 파일 첨부 (이미지)</t>
+          <t>계약·도서 파일 첨부 (이미지)</t>
         </is>
       </c>
       <c r="C32" s="171" t="inlineStr">
         <is>
-          <t>고해상도 PNG/JPG 화장품 제품 홍보 이미지 첨부</t>
+          <t>고해상도 PNG/JPG 전장부품 제품 조달 이미지 첨부</t>
         </is>
       </c>
       <c r="D32" s="198" t="n"/>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="C34" s="171" t="inlineStr">
         <is>
-          <t>시안 등록 후 AI 텍스트 추출 트리거</t>
+          <t>계약·도서 등록 후 AI 텍스트 추출 트리거</t>
         </is>
       </c>
       <c r="D34" s="198" t="n"/>
@@ -3626,13 +3626,13 @@
       </c>
       <c r="C35" s="171" t="inlineStr">
         <is>
-          <t>이미지 시안에 대해 OCR 비동기 워커 호출</t>
+          <t>이미지 계약·도서에 대해 OCR 비동기 워커 호출</t>
         </is>
       </c>
       <c r="D35" s="198" t="n"/>
       <c r="E35" s="171" t="inlineStr">
         <is>
-          <t>이미지 내 화장품 카피 문안 바운딩 박스(Bounding Box) 좌표 및 텍스트 추출</t>
+          <t>이미지 내 전장부품 조항 계약조항 바운딩 박스(Bounding Box) 좌표 및 텍스트 추출</t>
         </is>
       </c>
       <c r="F35" s="199" t="n"/>
@@ -3669,7 +3669,7 @@
       <c r="D36" s="198" t="n"/>
       <c r="E36" s="171" t="inlineStr">
         <is>
-          <t>완결된 문장 단위(Sentence Split)로 분리되어 24개 심의 대상 문장 생성</t>
+          <t>완결된 문장 단위(Sentence Split)로 분리되어 24개 검증 대상 문장 생성</t>
         </is>
       </c>
       <c r="F36" s="199" t="n"/>
@@ -3700,13 +3700,13 @@
       </c>
       <c r="C37" s="171" t="inlineStr">
         <is>
-          <t>의약품 오인 표현('여드름 치료', '염증 완치', '피부 재생') 포함 문안 주입</t>
+          <t>불공정 독소조항 표현('과전류 면책', '부식 전가', '전장부품 재생') 포함 계약조항 주입</t>
         </is>
       </c>
       <c r="D37" s="198" t="n"/>
       <c r="E37" s="171" t="inlineStr">
         <is>
-          <t>금지(BAN) 등급 즉시 분류 및 관련 법령(표시·광고 공정화법 제3조) 위반 태그 자동 부여</t>
+          <t>금지(BAN) 등급 즉시 분류 및 관련 법령(하도급법 제3조의4) 위반 태그 자동 부여</t>
         </is>
       </c>
       <c r="F37" s="199" t="n"/>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C38" s="171" t="inlineStr">
         <is>
-          <t>최고/유일 등 절대적 표현('국내 최초 100%', '부작용 0%') 포함 문안 주입</t>
+          <t>최고/유일 등 절대적 표현('국내 최초 100%', '부작용 0%') 포함 계약조항 주입</t>
         </is>
       </c>
       <c r="D38" s="198" t="n"/>
@@ -3769,25 +3769,25 @@
       </c>
       <c r="B39" s="170" t="inlineStr">
         <is>
-          <t>ProductLab 전성분·원료 배합한도 DB 연계 ([Option] KT레몬)</t>
+          <t>PLM-Nexus 자재BOM·원소재 유해물질한도 DB 연계 ([Option] HB-Monitor)</t>
         </is>
       </c>
       <c r="C39" s="171" t="inlineStr">
         <is>
-          <t>화장품 배합 성분('레티놀', '나이아신아마이드', 'EGF') 포함 문구 대조</t>
+          <t>전장부품 조성 성분('육가크롬(Cr6+)', '납(Pb)', '카드뮴(Cd)') 포함 조항 대조</t>
         </is>
       </c>
       <c r="D39" s="198" t="n"/>
       <c r="E39" s="171" t="inlineStr">
         <is>
-          <t>KT 레몬 API 실시간 호출을 통해 배합한도(예: 0.5% 이하) 준수 여부 자동 조회</t>
+          <t>HB-Monitor API 실시간 호출을 통해 유해물질한도(예: 0.5% 이하) 준수 여부 자동 조회</t>
         </is>
       </c>
       <c r="F39" s="199" t="n"/>
       <c r="G39" s="198" t="n"/>
       <c r="H39" s="171" t="inlineStr">
         <is>
-          <t>정상 (Pass) - 성분 배합기준 정상 연계 매핑</t>
+          <t>정상 (Pass) - 성분 조성기준 정상 연계 매핑</t>
         </is>
       </c>
       <c r="I39" s="199" t="n"/>
@@ -3806,18 +3806,18 @@
       </c>
       <c r="B40" s="170" t="inlineStr">
         <is>
-          <t>ProductLab 효능 실증자료 연계</t>
+          <t>PLM-Nexus 성능규격 시험성적서 연계</t>
         </is>
       </c>
       <c r="C40" s="171" t="inlineStr">
         <is>
-          <t>인체적용시험 효능 표현('모공 42% 축소', '4주 사용 주름 개선') 문구 대조</t>
+          <t>공인신뢰성시험 성능규격 표현('전력손실 42% 저감', '4주 사용 내진동 개선') 조항 대조</t>
         </is>
       </c>
       <c r="D40" s="198" t="n"/>
       <c r="E40" s="171" t="inlineStr">
         <is>
-          <t>ProductLab 인체적용시험 보고서 DB 자동 쿼리하여 매칭되는 실증 번호 탐색</t>
+          <t>PLM-Nexus 공인신뢰성시험 보고서 DB 자동 쿼리하여 매칭되는 시험검증 번호 탐색</t>
         </is>
       </c>
       <c r="F40" s="199" t="n"/>
@@ -3843,18 +3843,18 @@
       </c>
       <c r="B41" s="170" t="inlineStr">
         <is>
-          <t>2단계 RAG 검색 (처분사례)</t>
+          <t>2단계 RAG 검색 (심결사례)</t>
         </is>
       </c>
       <c r="C41" s="171" t="inlineStr">
         <is>
-          <t>애매하거나 유사 모호한 표현('피부 본연의 치유력 활성화') 입력</t>
+          <t>애매하거나 유사 모호한 표현('전장부품 본연의 배상력 활성화') 입력</t>
         </is>
       </c>
       <c r="D41" s="198" t="n"/>
       <c r="E41" s="171" t="inlineStr">
         <is>
-          <t>pgvector 코사인 유사도 검색으로 유사 식약처 행정처분 판례 3건 검색 및 임베딩 점수 도출</t>
+          <t>pgvector 코사인 유사도 검색으로 유사 공정위·표준원 하도급 심결례 3건 검색 및 임베딩 점수 도출</t>
         </is>
       </c>
       <c r="F41" s="199" t="n"/>
@@ -3880,18 +3880,18 @@
       </c>
       <c r="B42" s="170" t="inlineStr">
         <is>
-          <t>3단계 Agent 심의 (문맥 추론)</t>
+          <t>3단계 Agent 검증 (문맥 추론)</t>
         </is>
       </c>
       <c r="C42" s="171" t="inlineStr">
         <is>
-          <t>수식어가 포함된 복합 문맥 문장('피부 장벽을 건강하게 가꾸어주는 데 도움') 입력</t>
+          <t>수식어가 포함된 복합 문맥 문장('절연 내력을 건강하게 가꾸어주는 데 도움') 입력</t>
         </is>
       </c>
       <c r="D42" s="198" t="n"/>
       <c r="E42" s="171" t="inlineStr">
         <is>
-          <t>LLM 심의 에이전트가 완화 표현('가꾸어주는 데 도움') 인지하여 '안전(PASS)' 판정</t>
+          <t>LLM 검증 에이전트가 완화 표현('가꾸어주는 데 도움') 인지하여 '안전(PASS)' 판정</t>
         </is>
       </c>
       <c r="F42" s="199" t="n"/>
@@ -3959,20 +3959,20 @@
       </c>
       <c r="C44" s="171" t="inlineStr">
         <is>
-          <t>금지/주의 문장('피부 재생 효과 탁월')에 대한 대체 문안 요청</t>
+          <t>금지/주의 문장('전장부품 재생 효과 탁월')에 대한 대체 계약조항 요청</t>
         </is>
       </c>
       <c r="D44" s="198" t="n"/>
       <c r="E44" s="171" t="inlineStr">
         <is>
-          <t>'피부결 개선에 도움', '지친 피부를 건강하게 케어' 등 안전한 검증 표현 3종 추천</t>
+          <t>'납품일정 개선에 도움', '지친 전장부품를 건강하게 관리' 등 안전한 검증 표현 3종 추천</t>
         </is>
       </c>
       <c r="F44" s="199" t="n"/>
       <c r="G44" s="198" t="n"/>
       <c r="H44" s="171" t="inlineStr">
         <is>
-          <t>정상 (Pass) - 식약처 승인 안전 대체어 3건 제시</t>
+          <t>정상 (Pass) - 공정위·표준원 승인 안전 표준대안 3건 제시</t>
         </is>
       </c>
       <c r="I44" s="199" t="n"/>
@@ -3991,18 +3991,18 @@
       </c>
       <c r="B45" s="170" t="inlineStr">
         <is>
-          <t>심의 상세 콘솔 렌더링</t>
+          <t>검증 상세 콘솔 렌더링</t>
         </is>
       </c>
       <c r="C45" s="171" t="inlineStr">
         <is>
-          <t>마케터 화면에서 AI 판정 결과 상세 확인</t>
+          <t>구매담당자 화면에서 AI 판정 결과 상세 확인</t>
         </is>
       </c>
       <c r="D45" s="198" t="n"/>
       <c r="E45" s="171" t="inlineStr">
         <is>
-          <t>좌측 원본 시안(이미지/PPTX 바운딩 박스) ↔ 우측 문장별 판정 카드 Side-by-Side 렌더링</t>
+          <t>좌측 원본 계약·도서(이미지/PPTX 바운딩 박스) ↔ 우측 문장별 판정 카드 Side-by-Side 렌더링</t>
         </is>
       </c>
       <c r="F45" s="199" t="n"/>
@@ -4039,7 +4039,7 @@
       <c r="D46" s="198" t="n"/>
       <c r="E46" s="171" t="inlineStr">
         <is>
-          <t>좌측 시안 내 해당 텍스트 위치(바운딩 박스)로 자동 스크롤 및 붉은색 포커스 강조</t>
+          <t>좌측 계약·도서 내 해당 텍스트 위치(바운딩 박스)로 자동 스크롤 및 붉은색 포커스 강조</t>
         </is>
       </c>
       <c r="F46" s="199" t="n"/>
@@ -4070,20 +4070,20 @@
       </c>
       <c r="C47" s="171" t="inlineStr">
         <is>
-          <t>AI가 추천한 대체 문안 중 1순위 문안 '적용' 버튼 클릭</t>
+          <t>AI가 추천한 대체 계약조항 중 1순위 계약조항 '적용' 버튼 클릭</t>
         </is>
       </c>
       <c r="D47" s="198" t="n"/>
       <c r="E47" s="171" t="inlineStr">
         <is>
-          <t>심의 문안이 대체 표현으로 즉시 갱신되고 재판정 상태가 '안전'으로 전환</t>
+          <t>검증 계약조항이 대체 표현으로 즉시 갱신되고 재판정 상태가 '안전'으로 전환</t>
         </is>
       </c>
       <c r="F47" s="199" t="n"/>
       <c r="G47" s="198" t="n"/>
       <c r="H47" s="171" t="inlineStr">
         <is>
-          <t>정상 (Pass) - 대체 문안 치환 및 상태 갱신</t>
+          <t>정상 (Pass) - 대체 계약조항 치환 및 상태 갱신</t>
         </is>
       </c>
       <c r="I47" s="199" t="n"/>
@@ -4102,12 +4102,12 @@
       </c>
       <c r="B48" s="170" t="inlineStr">
         <is>
-          <t>마케터 소명 의견 작성</t>
+          <t>구매담당자 소명 의견 작성</t>
         </is>
       </c>
       <c r="C48" s="171" t="inlineStr">
         <is>
-          <t>실증자료 추가가 필요한 문장에 대해 시험성적서 첨부 및 소명 메모 입력</t>
+          <t>시험성적서 추가가 필요한 문장에 대해 시험성적서 첨부 및 소명 메모 입력</t>
         </is>
       </c>
       <c r="D48" s="198" t="n"/>
@@ -4139,25 +4139,25 @@
       </c>
       <c r="B49" s="170" t="inlineStr">
         <is>
-          <t>RA 전문가 심의 요청 제출</t>
+          <t>법무·QA 전문위원 검증 요청 제출</t>
         </is>
       </c>
       <c r="C49" s="171" t="inlineStr">
         <is>
-          <t>마케터가 1차 수정 및 검토 완료 후 'RA 심의 요청' 버튼 클릭</t>
+          <t>구매담당자가 1차 수정 및 검토 완료 후 'QA 검증 요청' 버튼 클릭</t>
         </is>
       </c>
       <c r="D49" s="198" t="n"/>
       <c r="E49" s="171" t="inlineStr">
         <is>
-          <t>심의 상태가 'REQUESTED(심의요청)'으로 변경되고 담당 RA 전문가에게 사내 알림 발송</t>
+          <t>검증 상태가 'REQUESTED(검증요청)'으로 변경되고 담당 법무·QA 전문위원에게 사내 알림 발송</t>
         </is>
       </c>
       <c r="F49" s="199" t="n"/>
       <c r="G49" s="198" t="n"/>
       <c r="H49" s="171" t="inlineStr">
         <is>
-          <t>정상 (Pass) - 심의 접수 상태 전환 및 알림 큐 전송</t>
+          <t>정상 (Pass) - 검증 접수 상태 전환 및 알림 큐 전송</t>
         </is>
       </c>
       <c r="I49" s="199" t="n"/>
@@ -4176,18 +4176,18 @@
       </c>
       <c r="B50" s="170" t="inlineStr">
         <is>
-          <t>RA 심의 접수 목록 조회</t>
+          <t>QA 검증 접수 목록 조회</t>
         </is>
       </c>
       <c r="C50" s="171" t="inlineStr">
         <is>
-          <t>RA 담당자 계정으로 로그인하여 '심의 접수 대기 목록' 조회</t>
+          <t>법무·QA 담당자 계정으로 로그인하여 '검증 접수 대기 목록' 조회</t>
         </is>
       </c>
       <c r="D50" s="198" t="n"/>
       <c r="E50" s="171" t="inlineStr">
         <is>
-          <t>방금 요청된 심의 건이 긴급도 및 위험도 뱃지와 함께 최상단에 노출</t>
+          <t>방금 요청된 검증 건이 긴급도 및 위험도 뱃지와 함께 최상단에 노출</t>
         </is>
       </c>
       <c r="F50" s="199" t="n"/>
@@ -4213,25 +4213,25 @@
       </c>
       <c r="B51" s="170" t="inlineStr">
         <is>
-          <t>RA 전문가 판정 콘솔 오픈</t>
+          <t>법무·QA 전문위원 판정 콘솔 오픈</t>
         </is>
       </c>
       <c r="C51" s="171" t="inlineStr">
         <is>
-          <t>접수된 심의 건 상세 화면 진입</t>
+          <t>접수된 검증 건 상세 화면 진입</t>
         </is>
       </c>
       <c r="D51" s="198" t="n"/>
       <c r="E51" s="171" t="inlineStr">
         <is>
-          <t>마케터 수정 이력, AI 3단계 판정 로그, KT레몬/ProductLab 연계 근거가 통합 뷰어로 제공</t>
+          <t>구매담당자 수정 이력, AI 3단계 판정 로그, HB-Monitor/PLM-Nexus 연계 근거가 통합 뷰어로 제공</t>
         </is>
       </c>
       <c r="F51" s="199" t="n"/>
       <c r="G51" s="198" t="n"/>
       <c r="H51" s="171" t="inlineStr">
         <is>
-          <t>정상 (Pass) - 전문가 심의 종합 콘솔 렌더링</t>
+          <t>정상 (Pass) - 전문가 검증 종합 콘솔 렌더링</t>
         </is>
       </c>
       <c r="I51" s="199" t="n"/>
@@ -4250,18 +4250,18 @@
       </c>
       <c r="B52" s="170" t="inlineStr">
         <is>
-          <t>RA 문장별 판정 오버라이드</t>
+          <t>QA 문장별 판정 오버라이드</t>
         </is>
       </c>
       <c r="C52" s="171" t="inlineStr">
         <is>
-          <t>AI가 '주의'로 판정한 문장에 대해 RA 전문가가 시험성적서 인정하여 '적합(PASS)'으로 변경</t>
+          <t>AI가 '주의'로 판정한 문장에 대해 법무·QA 전문위원가 시험성적서 인정하여 '적합(PASS)'으로 변경</t>
         </is>
       </c>
       <c r="D52" s="198" t="n"/>
       <c r="E52" s="171" t="inlineStr">
         <is>
-          <t>RA 의견 입력('2026 ProductLab 피부임상 데이터 확인 완료') 및 오버라이드 사유 기록</t>
+          <t>QA 의견 입력('2026 PLM-Nexus 전장부품신뢰성 데이터 확인 완료') 및 오버라이드 사유 기록</t>
         </is>
       </c>
       <c r="F52" s="199" t="n"/>
@@ -4287,18 +4287,18 @@
       </c>
       <c r="B53" s="170" t="inlineStr">
         <is>
-          <t>RA 수정 권고 작성</t>
+          <t>QA 수정 권고 작성</t>
         </is>
       </c>
       <c r="C53" s="171" t="inlineStr">
         <is>
-          <t>여전히 위험성이 있는 카피 문안에 대해 마케터 전달용 수정 가이드 작성</t>
+          <t>여전히 위험성이 있는 조항 계약조항에 대해 구매담당자 전달용 수정 가이드 작성</t>
         </is>
       </c>
       <c r="D53" s="198" t="n"/>
       <c r="E53" s="171" t="inlineStr">
         <is>
-          <t>권고 문구 '피부 장벽 케어' 입력 및 반려/수정 사유 등록</t>
+          <t>권고 조항 '정격 절연내력 기준 준수' 입력 및 반려/수정 사유 등록</t>
         </is>
       </c>
       <c r="F53" s="199" t="n"/>
@@ -4324,12 +4324,12 @@
       </c>
       <c r="B54" s="170" t="inlineStr">
         <is>
-          <t>최종 심의 확정 처리</t>
+          <t>최종 검증 확정 처리</t>
         </is>
       </c>
       <c r="C54" s="171" t="inlineStr">
         <is>
-          <t>모든 문안 검토 완료 후 '심의 확정(승인/조건부 승인)' 버튼 클릭</t>
+          <t>모든 계약 검토 완료 후 '검증 확정(승인/조건부 승인)' 버튼 클릭</t>
         </is>
       </c>
       <c r="D54" s="198" t="n"/>
@@ -4342,7 +4342,7 @@
       <c r="G54" s="198" t="n"/>
       <c r="H54" s="171" t="inlineStr">
         <is>
-          <t>정상 (Pass) - 심의 승인 완료 및 상태 불변 락 적용</t>
+          <t>정상 (Pass) - 검증 승인 완료 및 상태 불변 락 적용</t>
         </is>
       </c>
       <c r="I54" s="199" t="n"/>
@@ -4361,18 +4361,18 @@
       </c>
       <c r="B55" s="170" t="inlineStr">
         <is>
-          <t>심의 결과 리포트 PDF 자동 생성</t>
+          <t>검증 결과 리포트 PDF 자동 생성</t>
         </is>
       </c>
       <c r="C55" s="171" t="inlineStr">
         <is>
-          <t>심의 확정 즉시 PDF 엔진 비동기 호출</t>
+          <t>검증 확정 즉시 PDF 엔진 비동기 호출</t>
         </is>
       </c>
       <c r="D55" s="198" t="n"/>
       <c r="E55" s="171" t="inlineStr">
         <is>
-          <t>표지, 종합 판정, 문장별 대조표, 실증자료 목록, RA 승인 서명이 포함된 공문서 PDF 생성</t>
+          <t>표지, 종합 판정, 문장별 대조표, 시험성적서 목록, QA 승인 서명이 포함된 공문서 PDF 생성</t>
         </is>
       </c>
       <c r="F55" s="199" t="n"/>
@@ -4398,18 +4398,18 @@
       </c>
       <c r="B56" s="170" t="inlineStr">
         <is>
-          <t>MarketingHub 시스템 연계 회신</t>
+          <t>SRM-Portal 시스템 연계 회신</t>
         </is>
       </c>
       <c r="C56" s="171" t="inlineStr">
         <is>
-          <t>사내 MarketingHub 광고심의 시스템 REST API 엔드포인트 호출</t>
+          <t>사내 SRM-Portal 계약·규격검증 시스템 REST API 엔드포인트 호출</t>
         </is>
       </c>
       <c r="D56" s="198" t="n"/>
       <c r="E56" s="171" t="inlineStr">
         <is>
-          <t>심의의뢰번호, 최종 승인 결과, 위험도 스코어, PDF 리포트 다운로드 URL 페이로드 전송</t>
+          <t>검증요청번호, 최종 승인 결과, 위험도 스코어, PDF 리포트 다운로드 URL 페이로드 전송</t>
         </is>
       </c>
       <c r="F56" s="199" t="n"/>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="B57" s="170" t="inlineStr">
         <is>
-          <t>MarketingHub 연계 실패 시 재시도 처리</t>
+          <t>SRM-Portal 연계 실패 시 재시도 처리</t>
         </is>
       </c>
       <c r="C57" s="171" t="inlineStr">
         <is>
-          <t>MarketingHub 시스템 일시 장애(HTTP 503) 시뮬레이션</t>
+          <t>SRM-Portal 시스템 일시 장애(HTTP 503) 시뮬레이션</t>
         </is>
       </c>
       <c r="D57" s="198" t="n"/>
@@ -4477,13 +4477,13 @@
       </c>
       <c r="C58" s="171" t="inlineStr">
         <is>
-          <t>심의 완료 시점 데이터베이스 변경 트랜잭션 검증</t>
+          <t>검증 완료 시점 데이터베이스 변경 트랜잭션 검증</t>
         </is>
       </c>
       <c r="D58" s="198" t="n"/>
       <c r="E58" s="171" t="inlineStr">
         <is>
-          <t>요청자, 심의자, AI판정 원본, 오버라이드 내역, 일시, IP, SHA-256 해시 감사로그 적재</t>
+          <t>요청자, 검증자, AI판정 원본, 오버라이드 내역, 일시, IP, SHA-256 해시 감사로그 적재</t>
         </is>
       </c>
       <c r="F58" s="199" t="n"/>
@@ -4546,18 +4546,18 @@
       </c>
       <c r="B60" s="170" t="inlineStr">
         <is>
-          <t>심의 이력 버전 관리 조회</t>
+          <t>검증 이력 버전 관리 조회</t>
         </is>
       </c>
       <c r="C60" s="171" t="inlineStr">
         <is>
-          <t>심의 상세 화면에서 '이력 및 버전 비교' 탭 클릭</t>
+          <t>검증 상세 화면에서 '이력 및 버전 비교' 탭 클릭</t>
         </is>
       </c>
       <c r="D60" s="198" t="n"/>
       <c r="E60" s="171" t="inlineStr">
         <is>
-          <t>최초 업로드 시안(v1.0) ↔ 마케터 수정본(v1.1) ↔ RA 확정본(v1.2) 변경 내역 차분 뷰어 확인</t>
+          <t>최초 업로드 계약·도서(v1.0) ↔ 구매담당자 수정본(v1.1) ↔ QA 확정본(v1.2) 변경 내역 차분 뷰어 확인</t>
         </is>
       </c>
       <c r="F60" s="199" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="C61" s="171" t="inlineStr">
         <is>
-          <t>관리자 콘솔에서 신규 금지어('엑소좀 줄기세포') 및 처분근거 등록</t>
+          <t>관리자 콘솔에서 신규 독소조항('엑소좀 줄기배상한도') 및 처분근거 등록</t>
         </is>
       </c>
       <c r="D61" s="198" t="n"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="C62" s="171" t="inlineStr">
         <is>
-          <t>관리자 콘솔에서 최신 식약처 행정처분 공문(PDF) 1건 업로드</t>
+          <t>관리자 콘솔에서 최신 공정위·표준원 시정명령·심결 공문(PDF) 1건 업로드</t>
         </is>
       </c>
       <c r="D62" s="198" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C63" s="171" t="inlineStr">
         <is>
-          <t>100건의 표준 화장품 광고 문안 골든셋 일괄 평가 실행</t>
+          <t>100건의 표준 전장부품 구매계약 계약조항 골든셋 일괄 평가 실행</t>
         </is>
       </c>
       <c r="D63" s="198" t="n"/>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C64" s="171" t="inlineStr">
         <is>
-          <t>마케터 계정으로 관리자 설정 메뉴(/admin) 직접 URL 호출 시도</t>
+          <t>구매담당자 계정으로 관리자 설정 메뉴(/admin) 직접 URL 호출 시도</t>
         </is>
       </c>
       <c r="D64" s="198" t="n"/>
@@ -4731,12 +4731,12 @@
       </c>
       <c r="B65" s="170" t="inlineStr">
         <is>
-          <t>동시 심의 트랜잭션 격리</t>
+          <t>동시 검증 트랜잭션 격리</t>
         </is>
       </c>
       <c r="C65" s="171" t="inlineStr">
         <is>
-          <t>동일한 심의 의뢰 건에 대해 2명의 사용자가 동시 수정/승인 요청 시도</t>
+          <t>동일한 검증 요청 건에 대해 2명의 사용자가 동시 수정/승인 요청 시도</t>
         </is>
       </c>
       <c r="D65" s="198" t="n"/>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="C66" s="171" t="inlineStr">
         <is>
-          <t>10개 제품 상세페이지 시안(총 50개 이미지) 동시 일괄 심의 의뢰</t>
+          <t>10개 제품 기술시방서 계약·도서(총 50개 이미지) 동시 일괄 검증 요청</t>
         </is>
       </c>
       <c r="D66" s="198" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="B68" s="170" t="inlineStr">
         <is>
-          <t>심의 완료 통계 및 KPI 리포트</t>
+          <t>검증 완료 통계 및 KPI 리포트</t>
         </is>
       </c>
       <c r="C68" s="171" t="inlineStr">
@@ -4853,7 +4853,7 @@
       <c r="D68" s="198" t="n"/>
       <c r="E68" s="171" t="inlineStr">
         <is>
-          <t>브랜드별 심의 건수, 고위험 카피 빈도 순위, 평균 심의 소요 시간(12분) 통계 차트 조회</t>
+          <t>사업부별 검증 건수, 고위험 조항 빈도 순위, 평균 검증 소요 시간(12분) 통계 차트 조회</t>
         </is>
       </c>
       <c r="F68" s="199" t="n"/>
